--- a/Excel9to10/Lec - 4.2.xlsx
+++ b/Excel9to10/Lec - 4.2.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiten\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllData\Excel9to10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745BA0E9-7CC6-4A2D-9850-DAEC42B15F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315B7F1F-6790-40A7-A31D-8594DCD64FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6C2C9399-45F9-4682-AC1B-4E221ED87509}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6C2C9399-45F9-4682-AC1B-4E221ED87509}"/>
   </bookViews>
   <sheets>
     <sheet name="Theory" sheetId="4" r:id="rId1"/>
     <sheet name="Pizza Price Prediction" sheetId="3" r:id="rId2"/>
     <sheet name="Lemonade Sold Prediction" sheetId="1" r:id="rId3"/>
-    <sheet name="House Price Prediction" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="House Price Prediction" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -32,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="82">
   <si>
     <r>
       <rPr>
@@ -329,6 +334,135 @@
   <si>
     <t>House Size (sq. ft.)</t>
   </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>SUMMARY OUTPUT</t>
+  </si>
+  <si>
+    <t>Regression Statistics</t>
+  </si>
+  <si>
+    <t>Multiple R</t>
+  </si>
+  <si>
+    <t>R Square</t>
+  </si>
+  <si>
+    <t>Adjusted R Square</t>
+  </si>
+  <si>
+    <t>Standard Error</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>t Stat</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>Lower 95%</t>
+  </si>
+  <si>
+    <t>Upper 95%</t>
+  </si>
+  <si>
+    <t>Lower 95.0%</t>
+  </si>
+  <si>
+    <t>Upper 95.0%</t>
+  </si>
+  <si>
+    <t>X Variable 1</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Standard Deviation</t>
+  </si>
+  <si>
+    <t>Sample Variance</t>
+  </si>
+  <si>
+    <t>Kurtosis</t>
+  </si>
+  <si>
+    <t>Skewness</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Largest(1)</t>
+  </si>
+  <si>
+    <t>Smallest(1)</t>
+  </si>
+  <si>
+    <t>Confidence Level(95.0%)</t>
+  </si>
 </sst>
 </file>
 
@@ -338,7 +472,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,6 +536,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -435,7 +577,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -580,11 +722,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -665,6 +827,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -697,6 +862,14 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1033,106 +1206,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BC107E-77C4-4964-9868-836DABB3D59D}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="14"/>
     </row>
-    <row r="2" spans="1:2" ht="80.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="80.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:2" ht="27" x14ac:dyDescent="0.25">
       <c r="B4" s="22" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="6"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="15"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="15"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="28" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="29"/>
       <c r="B17" s="21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="21"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="28" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="29"/>
       <c r="B20" s="21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
     </row>
   </sheetData>
@@ -1147,29 +1320,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4ED941-A439-4368-BF6F-884C4441C0A2}">
   <dimension ref="A1:S39"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.109375" style="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>14</v>
       </c>
@@ -1179,16 +1352,16 @@
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
@@ -1196,18 +1369,18 @@
         <v>17</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-    </row>
-    <row r="3" spans="1:12" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+    </row>
+    <row r="3" spans="1:12" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1242,159 +1415,263 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>8</v>
       </c>
       <c r="B4" s="16">
         <v>280</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="32"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C4" s="18">
+        <f>$F$12*A4+$F$13</f>
+        <v>221.91588785046724</v>
+      </c>
+      <c r="E4" s="33">
+        <f>AVERAGE(A4:A7)</f>
+        <v>11.25</v>
+      </c>
+      <c r="F4" s="36">
+        <f>AVERAGE(B4:B7)</f>
+        <v>651.25</v>
+      </c>
+      <c r="G4" s="3">
+        <f>A4-$E$4</f>
+        <v>-3.25</v>
+      </c>
+      <c r="H4" s="12">
+        <f>B4-$F$4</f>
+        <v>-371.25</v>
+      </c>
+      <c r="I4" s="12">
+        <f>G4*H4</f>
+        <v>1206.5625</v>
+      </c>
+      <c r="J4" s="36">
+        <f>SUM(I4:I7)</f>
+        <v>3533.75</v>
+      </c>
+      <c r="K4" s="3">
+        <f>G4*G4</f>
+        <v>10.5625</v>
+      </c>
+      <c r="L4" s="33">
+        <f>SUM(K4:K7)</f>
+        <v>26.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>10</v>
       </c>
       <c r="B5" s="16">
         <v>450</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="33"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="18">
+        <f t="shared" ref="C5:C12" si="0">$F$12*A5+$F$13</f>
+        <v>486.12149532710282</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="3">
+        <f t="shared" ref="G5:G7" si="1">A5-$E$4</f>
+        <v>-1.25</v>
+      </c>
+      <c r="H5" s="12">
+        <f t="shared" ref="H5:H7" si="2">B5-$F$4</f>
+        <v>-201.25</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" ref="I5:I7" si="3">G5*H5</f>
+        <v>251.5625</v>
+      </c>
+      <c r="J5" s="34"/>
+      <c r="K5" s="3">
+        <f t="shared" ref="K5:K7" si="4">G5*G5</f>
+        <v>1.5625</v>
+      </c>
+      <c r="L5" s="34"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>12</v>
       </c>
       <c r="B6" s="16">
         <v>675</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="33"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="18">
+        <f t="shared" si="0"/>
+        <v>750.32710280373817</v>
+      </c>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="3">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="12">
+        <f t="shared" si="2"/>
+        <v>23.75</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="3"/>
+        <v>17.8125</v>
+      </c>
+      <c r="J6" s="34"/>
+      <c r="K6" s="3">
+        <f t="shared" si="4"/>
+        <v>0.5625</v>
+      </c>
+      <c r="L6" s="34"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>15</v>
       </c>
       <c r="B7" s="16">
         <v>1200</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="34"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="18">
+        <f t="shared" si="0"/>
+        <v>1146.6355140186915</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="3">
+        <f t="shared" si="1"/>
+        <v>3.75</v>
+      </c>
+      <c r="H7" s="12">
+        <f t="shared" si="2"/>
+        <v>548.75</v>
+      </c>
+      <c r="I7" s="12">
+        <f t="shared" si="3"/>
+        <v>2057.8125</v>
+      </c>
+      <c r="J7" s="35"/>
+      <c r="K7" s="3">
+        <f t="shared" si="4"/>
+        <v>14.0625</v>
+      </c>
+      <c r="L7" s="35"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>17</v>
       </c>
       <c r="B8" s="26">
         <v>1410.8411214953269</v>
       </c>
-      <c r="C8" s="18"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="18">
+        <f t="shared" si="0"/>
+        <v>1410.8411214953269</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>18</v>
       </c>
       <c r="B9" s="26">
         <v>1542.9439252336449</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="E9" s="30" t="s">
+      <c r="C9" s="18">
+        <f t="shared" si="0"/>
+        <v>1542.9439252336449</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>20</v>
       </c>
       <c r="B10" s="26">
         <v>1807.1495327102805</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="E10" s="30" t="s">
+      <c r="C10" s="18">
+        <f t="shared" si="0"/>
+        <v>1807.1495327102805</v>
+      </c>
+      <c r="E10" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>22</v>
       </c>
       <c r="B11" s="26">
         <v>2071.3551401869163</v>
       </c>
-      <c r="C11" s="18"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="18">
+        <f t="shared" si="0"/>
+        <v>2071.3551401869163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>26</v>
       </c>
       <c r="B12" s="26">
         <v>2599.7663551401865</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="18">
+        <f t="shared" si="0"/>
+        <v>2599.7663551401865</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="12">
+        <f>J4/L4</f>
+        <v>132.10280373831776</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E13" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="28">
+        <f>F4-F12*E4</f>
+        <v>-834.90654205607484</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E16" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="12"/>
+      <c r="F16" s="12">
+        <f>SLOPE(B4:B7,A4:A7)</f>
+        <v>132.10280373831776</v>
+      </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
     </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="12"/>
+      <c r="F17" s="12">
+        <f>INTERCEPT(B4:B7,A4:A7)</f>
+        <v>-834.90654205607484</v>
+      </c>
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17"/>
@@ -1402,7 +1679,7 @@
       <c r="K17"/>
       <c r="L17"/>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18"/>
@@ -1414,7 +1691,7 @@
       <c r="K18"/>
       <c r="L18"/>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
@@ -1433,7 +1710,7 @@
       <c r="R19"/>
       <c r="S19"/>
     </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
@@ -1452,7 +1729,7 @@
       <c r="R20"/>
       <c r="S20"/>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
@@ -1471,7 +1748,7 @@
       <c r="R21"/>
       <c r="S21"/>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
@@ -1490,7 +1767,7 @@
       <c r="R22"/>
       <c r="S22"/>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
@@ -1509,7 +1786,7 @@
       <c r="R23"/>
       <c r="S23"/>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
@@ -1528,7 +1805,7 @@
       <c r="R24"/>
       <c r="S24"/>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25"/>
@@ -1547,7 +1824,7 @@
       <c r="R25"/>
       <c r="S25"/>
     </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -1566,7 +1843,7 @@
       <c r="R26"/>
       <c r="S26"/>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -1585,7 +1862,7 @@
       <c r="R27"/>
       <c r="S27"/>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -1604,7 +1881,7 @@
       <c r="R28"/>
       <c r="S28"/>
     </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -1623,7 +1900,7 @@
       <c r="R29"/>
       <c r="S29"/>
     </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30"/>
@@ -1642,7 +1919,7 @@
       <c r="R30"/>
       <c r="S30"/>
     </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
@@ -1661,7 +1938,7 @@
       <c r="R31"/>
       <c r="S31"/>
     </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
@@ -1680,7 +1957,7 @@
       <c r="R32"/>
       <c r="S32"/>
     </row>
-    <row r="33" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1699,7 +1976,7 @@
       <c r="R33"/>
       <c r="S33"/>
     </row>
-    <row r="34" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1718,7 +1995,7 @@
       <c r="R34"/>
       <c r="S34"/>
     </row>
-    <row r="35" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
@@ -1737,7 +2014,7 @@
       <c r="R35"/>
       <c r="S35"/>
     </row>
-    <row r="36" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36"/>
@@ -1755,7 +2032,7 @@
       <c r="R36"/>
       <c r="S36"/>
     </row>
-    <row r="37" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:19" x14ac:dyDescent="0.25">
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37"/>
@@ -1773,7 +2050,7 @@
       <c r="R37"/>
       <c r="S37"/>
     </row>
-    <row r="38" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:19" x14ac:dyDescent="0.25">
       <c r="D38"/>
       <c r="E38"/>
       <c r="F38"/>
@@ -1791,7 +2068,7 @@
       <c r="R38"/>
       <c r="S38"/>
     </row>
-    <row r="39" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:19" x14ac:dyDescent="0.25">
       <c r="K39"/>
       <c r="L39"/>
       <c r="M39"/>
@@ -1820,24 +2097,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD2AA26-B4D9-4C1D-9CC2-9236F00034BD}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="1"/>
+    <col min="9" max="9" width="11.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>32</v>
       </c>
@@ -1847,16 +2124,16 @@
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-    </row>
-    <row r="2" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+    </row>
+    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>34</v>
       </c>
@@ -1866,25 +2143,28 @@
       <c r="C2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-    </row>
-    <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+    </row>
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>25</v>
       </c>
       <c r="B3" s="2">
         <v>50</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="2">
+        <f>$F$12*A3+$F$13</f>
+        <v>50</v>
+      </c>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -1910,130 +2190,225 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>30</v>
       </c>
       <c r="B4" s="2">
         <v>70</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="32"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C4" s="2">
+        <f t="shared" ref="C4:C10" si="0">$F$12*A4+$F$13</f>
+        <v>70</v>
+      </c>
+      <c r="E4" s="33">
+        <f>AVERAGE(A3:A6)</f>
+        <v>32.5</v>
+      </c>
+      <c r="F4" s="37">
+        <f>AVERAGE(B3:B6)</f>
+        <v>80</v>
+      </c>
+      <c r="G4" s="3">
+        <f>A3-$E$4</f>
+        <v>-7.5</v>
+      </c>
+      <c r="H4" s="19">
+        <f>B3-$F$4</f>
+        <v>-30</v>
+      </c>
+      <c r="I4" s="19">
+        <f>G4*H4</f>
+        <v>225</v>
+      </c>
+      <c r="J4" s="37">
+        <f>SUM(I4:I7)</f>
+        <v>500</v>
+      </c>
+      <c r="K4" s="3">
+        <f>G4*G4</f>
+        <v>56.25</v>
+      </c>
+      <c r="L4" s="33">
+        <f>SUM(K4:K7)</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>35</v>
       </c>
       <c r="B5" s="2">
         <v>90</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="33"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="2">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="3">
+        <f t="shared" ref="G5:G7" si="1">A4-$E$4</f>
+        <v>-2.5</v>
+      </c>
+      <c r="H5" s="19">
+        <f t="shared" ref="H5:H7" si="2">B4-$F$4</f>
+        <v>-10</v>
+      </c>
+      <c r="I5" s="19">
+        <f t="shared" ref="I5:I7" si="3">G5*H5</f>
+        <v>25</v>
+      </c>
+      <c r="J5" s="38"/>
+      <c r="K5" s="3">
+        <f t="shared" ref="K5:K7" si="4">G5*G5</f>
+        <v>6.25</v>
+      </c>
+      <c r="L5" s="34"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>40</v>
       </c>
       <c r="B6" s="2">
         <v>110</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="33"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="E6" s="34"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="3">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="19">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="I6" s="19">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="J6" s="38"/>
+      <c r="K6" s="3">
+        <f t="shared" si="4"/>
+        <v>6.25</v>
+      </c>
+      <c r="L6" s="34"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>42</v>
       </c>
       <c r="B7" s="27">
         <v>118</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="34"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="2">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="3">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="H7" s="19">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="I7" s="19">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+      <c r="J7" s="39"/>
+      <c r="K7" s="3">
+        <f t="shared" si="4"/>
+        <v>56.25</v>
+      </c>
+      <c r="L7" s="35"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>44</v>
       </c>
       <c r="B8" s="27">
         <v>126</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="2">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45</v>
       </c>
       <c r="B9" s="27">
         <v>130</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="E9" s="30" t="s">
+      <c r="C9" s="2">
+        <f t="shared" si="0"/>
+        <v>130</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>47</v>
       </c>
       <c r="B10" s="27">
         <v>138</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="E10" s="30" t="s">
+      <c r="C10" s="2">
+        <f t="shared" si="0"/>
+        <v>138</v>
+      </c>
+      <c r="E10" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E12" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="19"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F12" s="19">
+        <f>J4/L4</f>
+        <v>4</v>
+      </c>
+      <c r="G12" s="1">
+        <f>SLOPE(B3:B6,A3:A6)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="19"/>
+      <c r="F13" s="19">
+        <f>F4-F12*E4</f>
+        <v>-50</v>
+      </c>
+      <c r="G13" s="1">
+        <f>INTERCEPT(B3:B6,A3:A6)</f>
+        <v>-50</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2051,26 +2426,409 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9F4249-9A10-4099-A5EF-96C04024123D}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="43"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="42"/>
+      <c r="B11" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="40">
+        <v>1</v>
+      </c>
+      <c r="C12" s="40">
+        <v>1250000000000</v>
+      </c>
+      <c r="D12" s="40">
+        <v>1250000000000</v>
+      </c>
+      <c r="E12" s="40" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F12" s="40" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="40">
+        <v>2</v>
+      </c>
+      <c r="C13" s="40">
+        <v>0</v>
+      </c>
+      <c r="D13" s="40">
+        <v>0</v>
+      </c>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="41">
+        <v>3</v>
+      </c>
+      <c r="C14" s="41">
+        <v>1250000000000</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="42"/>
+      <c r="B16" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="40">
+        <v>1000000.0000000002</v>
+      </c>
+      <c r="C17" s="40">
+        <v>0</v>
+      </c>
+      <c r="D17" s="40">
+        <v>65535</v>
+      </c>
+      <c r="E17" s="40" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F17" s="40">
+        <v>1000000.0000000002</v>
+      </c>
+      <c r="G17" s="40">
+        <v>1000000.0000000002</v>
+      </c>
+      <c r="H17" s="40">
+        <v>1000000.0000000002</v>
+      </c>
+      <c r="I17" s="40">
+        <v>1000000.0000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="41">
+        <v>999.99999999999989</v>
+      </c>
+      <c r="C18" s="41">
+        <v>0</v>
+      </c>
+      <c r="D18" s="41">
+        <v>65535</v>
+      </c>
+      <c r="E18" s="41" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F18" s="41">
+        <v>999.99999999999989</v>
+      </c>
+      <c r="G18" s="41">
+        <v>999.99999999999989</v>
+      </c>
+      <c r="H18" s="41">
+        <v>999.99999999999989</v>
+      </c>
+      <c r="I18" s="41">
+        <v>999.99999999999989</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A61215D-F91C-48D4-BE1F-34957969D662}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="43"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="40">
+        <v>2443.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="40">
+        <v>309.87288580503918</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="40">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="40" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="40">
+        <v>876.45287543435154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="40">
+        <v>768169.64285714284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="40">
+        <v>-0.8583804351358113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="40">
+        <v>-0.57072335204024938</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="40">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="40">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="40">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="40">
+        <v>19550</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="40">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="40">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="41">
+        <v>732.73294068563723</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46914AF4-EE69-47FE-BD37-807D0CDE2794}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="1"/>
+    <col min="10" max="10" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>37</v>
       </c>
@@ -2080,16 +2838,16 @@
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -2099,18 +2857,18 @@
       <c r="C2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-    </row>
-    <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+    </row>
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1000</v>
       </c>
@@ -2143,7 +2901,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1500</v>
       </c>
@@ -2151,16 +2909,16 @@
         <v>2500000</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="35"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="3"/>
       <c r="H4" s="25"/>
       <c r="I4" s="12"/>
-      <c r="J4" s="35"/>
+      <c r="J4" s="36"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="32"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L4" s="33"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2000</v>
       </c>
@@ -2168,16 +2926,16 @@
         <v>3000000</v>
       </c>
       <c r="C5" s="18"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
       <c r="G5" s="3"/>
       <c r="H5" s="25"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="33"/>
+      <c r="J5" s="34"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="33"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L5" s="34"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2500</v>
       </c>
@@ -2185,16 +2943,16 @@
         <v>3500000</v>
       </c>
       <c r="C6" s="18"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="3"/>
       <c r="H6" s="25"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="33"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="33"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L6" s="34"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2800</v>
       </c>
@@ -2202,16 +2960,16 @@
         <v>3800000</v>
       </c>
       <c r="C7" s="18"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
       <c r="G7" s="3"/>
       <c r="H7" s="25"/>
       <c r="I7" s="12"/>
-      <c r="J7" s="34"/>
+      <c r="J7" s="35"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="34"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L7" s="35"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>3000</v>
       </c>
@@ -2220,7 +2978,7 @@
       </c>
       <c r="C8" s="18"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>3250</v>
       </c>
@@ -2228,17 +2986,17 @@
         <v>4250000</v>
       </c>
       <c r="C9" s="18"/>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3500</v>
       </c>
@@ -2246,23 +3004,23 @@
         <v>4500000</v>
       </c>
       <c r="C10" s="18"/>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E12" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E13" s="20" t="s">
         <v>31</v>
       </c>

--- a/Excel9to10/Lec - 4.2.xlsx
+++ b/Excel9to10/Lec - 4.2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllData\Excel9to10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315B7F1F-6790-40A7-A31D-8594DCD64FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACFBE36-B55F-479C-80E5-0CD57DB65F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6C2C9399-45F9-4682-AC1B-4E221ED87509}"/>
   </bookViews>
@@ -16,9 +16,7 @@
     <sheet name="Theory" sheetId="4" r:id="rId1"/>
     <sheet name="Pizza Price Prediction" sheetId="3" r:id="rId2"/>
     <sheet name="Lemonade Sold Prediction" sheetId="1" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
-    <sheet name="House Price Prediction" sheetId="2" r:id="rId6"/>
+    <sheet name="House Price Prediction" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
   <si>
     <r>
       <rPr>
@@ -340,129 +338,6 @@
   <si>
     <t>C</t>
   </si>
-  <si>
-    <t>SUMMARY OUTPUT</t>
-  </si>
-  <si>
-    <t>Regression Statistics</t>
-  </si>
-  <si>
-    <t>Multiple R</t>
-  </si>
-  <si>
-    <t>R Square</t>
-  </si>
-  <si>
-    <t>Adjusted R Square</t>
-  </si>
-  <si>
-    <t>Standard Error</t>
-  </si>
-  <si>
-    <t>Observations</t>
-  </si>
-  <si>
-    <t>ANOVA</t>
-  </si>
-  <si>
-    <t>Regression</t>
-  </si>
-  <si>
-    <t>Residual</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Intercept</t>
-  </si>
-  <si>
-    <t>df</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Significance F</t>
-  </si>
-  <si>
-    <t>Coefficients</t>
-  </si>
-  <si>
-    <t>t Stat</t>
-  </si>
-  <si>
-    <t>P-value</t>
-  </si>
-  <si>
-    <t>Lower 95%</t>
-  </si>
-  <si>
-    <t>Upper 95%</t>
-  </si>
-  <si>
-    <t>Lower 95.0%</t>
-  </si>
-  <si>
-    <t>Upper 95.0%</t>
-  </si>
-  <si>
-    <t>X Variable 1</t>
-  </si>
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Mean</t>
-  </si>
-  <si>
-    <t>Median</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>Standard Deviation</t>
-  </si>
-  <si>
-    <t>Sample Variance</t>
-  </si>
-  <si>
-    <t>Kurtosis</t>
-  </si>
-  <si>
-    <t>Skewness</t>
-  </si>
-  <si>
-    <t>Range</t>
-  </si>
-  <si>
-    <t>Minimum</t>
-  </si>
-  <si>
-    <t>Maximum</t>
-  </si>
-  <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Largest(1)</t>
-  </si>
-  <si>
-    <t>Smallest(1)</t>
-  </si>
-  <si>
-    <t>Confidence Level(95.0%)</t>
-  </si>
 </sst>
 </file>
 
@@ -472,7 +347,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,14 +411,6 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -577,7 +444,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -722,31 +589,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -862,14 +709,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1206,71 +1045,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BC107E-77C4-4964-9868-836DABB3D59D}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1">
       <c r="B1" s="14"/>
     </row>
-    <row r="2" spans="1:2" ht="80.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="80.25" customHeight="1" thickTop="1">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:2" ht="27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="37.5" customHeight="1" thickBot="1"/>
+    <row r="4" spans="1:2" ht="27">
       <c r="B4" s="22" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" s="6"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="B7" s="8"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="15">
       <c r="B8" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15">
       <c r="B9" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="15">
       <c r="B10" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="15.75" thickBot="1">
       <c r="B11" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="15">
       <c r="B12" s="15"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="15">
       <c r="B13" s="15"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="15">
       <c r="A15" s="3"/>
       <c r="B15" s="20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="15">
       <c r="A16" s="29" t="s">
         <v>8</v>
       </c>
@@ -1278,17 +1117,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15">
       <c r="A17" s="29"/>
       <c r="B17" s="21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="3"/>
       <c r="B18" s="21"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="29" t="s">
         <v>11</v>
       </c>
@@ -1296,16 +1135,16 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="29"/>
       <c r="B20" s="21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="B22" s="5"/>
     </row>
   </sheetData>
@@ -1320,29 +1159,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4ED941-A439-4368-BF6F-884C4441C0A2}">
   <dimension ref="A1:S39"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="1"/>
+    <col min="5" max="5" width="13.75" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.25" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="12.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="42" customHeight="1">
       <c r="A1" s="23" t="s">
         <v>14</v>
       </c>
@@ -1361,7 +1200,7 @@
       <c r="K1" s="30"/>
       <c r="L1" s="30"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
@@ -1380,7 +1219,7 @@
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
     </row>
-    <row r="3" spans="1:12" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="11" customFormat="1" ht="45">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1415,17 +1254,14 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" s="2">
         <v>8</v>
       </c>
       <c r="B4" s="16">
         <v>280</v>
       </c>
-      <c r="C4" s="18">
-        <f>$F$12*A4+$F$13</f>
-        <v>221.91588785046724</v>
-      </c>
+      <c r="C4" s="18"/>
       <c r="E4" s="33">
         <f>AVERAGE(A4:A7)</f>
         <v>11.25</v>
@@ -1459,123 +1295,110 @@
         <v>26.75</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" s="2">
         <v>10</v>
       </c>
       <c r="B5" s="16">
         <v>450</v>
       </c>
-      <c r="C5" s="18">
-        <f t="shared" ref="C5:C12" si="0">$F$12*A5+$F$13</f>
-        <v>486.12149532710282</v>
-      </c>
+      <c r="C5" s="18"/>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
       <c r="G5" s="3">
-        <f t="shared" ref="G5:G7" si="1">A5-$E$4</f>
+        <f t="shared" ref="G5:G7" si="0">A5-$E$4</f>
         <v>-1.25</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" ref="H5:H7" si="2">B5-$F$4</f>
+        <f t="shared" ref="H5:H7" si="1">B5-$F$4</f>
         <v>-201.25</v>
       </c>
       <c r="I5" s="12">
-        <f t="shared" ref="I5:I7" si="3">G5*H5</f>
+        <f t="shared" ref="I5:I7" si="2">G5*H5</f>
         <v>251.5625</v>
       </c>
       <c r="J5" s="34"/>
       <c r="K5" s="3">
-        <f t="shared" ref="K5:K7" si="4">G5*G5</f>
+        <f t="shared" ref="K5:K7" si="3">G5*G5</f>
         <v>1.5625</v>
       </c>
       <c r="L5" s="34"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" s="2">
         <v>12</v>
       </c>
       <c r="B6" s="16">
         <v>675</v>
       </c>
-      <c r="C6" s="18">
-        <f t="shared" si="0"/>
-        <v>750.32710280373817</v>
-      </c>
+      <c r="C6" s="18"/>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
       <c r="G6" s="3">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="12">
         <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-      <c r="H6" s="12">
+        <v>23.75</v>
+      </c>
+      <c r="I6" s="12">
         <f t="shared" si="2"/>
-        <v>23.75</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="3"/>
         <v>17.8125</v>
       </c>
       <c r="J6" s="34"/>
       <c r="K6" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.5625</v>
       </c>
       <c r="L6" s="34"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" s="2">
         <v>15</v>
       </c>
       <c r="B7" s="16">
         <v>1200</v>
       </c>
-      <c r="C7" s="18">
-        <f t="shared" si="0"/>
-        <v>1146.6355140186915</v>
-      </c>
+      <c r="C7" s="18"/>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
       <c r="G7" s="3">
+        <f t="shared" si="0"/>
+        <v>3.75</v>
+      </c>
+      <c r="H7" s="12">
         <f t="shared" si="1"/>
-        <v>3.75</v>
-      </c>
-      <c r="H7" s="12">
+        <v>548.75</v>
+      </c>
+      <c r="I7" s="12">
         <f t="shared" si="2"/>
-        <v>548.75</v>
-      </c>
-      <c r="I7" s="12">
-        <f t="shared" si="3"/>
         <v>2057.8125</v>
       </c>
       <c r="J7" s="35"/>
       <c r="K7" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>14.0625</v>
       </c>
       <c r="L7" s="35"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" s="3">
         <v>17</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="26"/>
+      <c r="C8" s="18">
+        <f>$F$12*A8+$F$13</f>
         <v>1410.8411214953269</v>
       </c>
-      <c r="C8" s="18">
-        <f t="shared" si="0"/>
-        <v>1410.8411214953269</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:12" ht="15">
       <c r="A9" s="3">
         <v>18</v>
       </c>
-      <c r="B9" s="26">
-        <v>1542.9439252336449</v>
-      </c>
+      <c r="B9" s="26"/>
       <c r="C9" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C9:C12" si="4">$F$12*A9+$F$13</f>
         <v>1542.9439252336449</v>
       </c>
       <c r="E9" s="31" t="s">
@@ -1588,15 +1411,13 @@
       <c r="J9" s="31"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15">
       <c r="A10" s="3">
         <v>20</v>
       </c>
-      <c r="B10" s="26">
-        <v>1807.1495327102805</v>
-      </c>
+      <c r="B10" s="26"/>
       <c r="C10" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1807.1495327102805</v>
       </c>
       <c r="E10" s="31" t="s">
@@ -1609,27 +1430,23 @@
       <c r="J10" s="31"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12">
       <c r="A11" s="3">
         <v>22</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="26"/>
+      <c r="C11" s="18">
+        <f t="shared" si="4"/>
         <v>2071.3551401869163</v>
       </c>
-      <c r="C11" s="18">
-        <f t="shared" si="0"/>
-        <v>2071.3551401869163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="3">
         <v>26</v>
       </c>
-      <c r="B12" s="26">
-        <v>2599.7663551401865</v>
-      </c>
+      <c r="B12" s="26"/>
       <c r="C12" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2599.7663551401865</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1640,7 +1457,7 @@
         <v>132.10280373831776</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15">
       <c r="E13" s="20" t="s">
         <v>40</v>
       </c>
@@ -1649,7 +1466,7 @@
         <v>-834.90654205607484</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15">
       <c r="E16" s="20" t="s">
         <v>30</v>
       </c>
@@ -1662,7 +1479,7 @@
       <c r="J16"/>
       <c r="K16"/>
     </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:19" ht="15">
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17" s="20" t="s">
@@ -1679,7 +1496,7 @@
       <c r="K17"/>
       <c r="L17"/>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:19">
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18"/>
@@ -1691,7 +1508,7 @@
       <c r="K18"/>
       <c r="L18"/>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:19">
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
@@ -1710,7 +1527,7 @@
       <c r="R19"/>
       <c r="S19"/>
     </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:19">
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
@@ -1729,7 +1546,7 @@
       <c r="R20"/>
       <c r="S20"/>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:19">
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
@@ -1748,7 +1565,7 @@
       <c r="R21"/>
       <c r="S21"/>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:19">
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
@@ -1767,7 +1584,7 @@
       <c r="R22"/>
       <c r="S22"/>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:19">
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
@@ -1786,7 +1603,7 @@
       <c r="R23"/>
       <c r="S23"/>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:19">
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
@@ -1805,7 +1622,7 @@
       <c r="R24"/>
       <c r="S24"/>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:19">
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25"/>
@@ -1824,7 +1641,7 @@
       <c r="R25"/>
       <c r="S25"/>
     </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:19">
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -1843,7 +1660,7 @@
       <c r="R26"/>
       <c r="S26"/>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:19">
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -1862,7 +1679,7 @@
       <c r="R27"/>
       <c r="S27"/>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:19">
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -1881,7 +1698,7 @@
       <c r="R28"/>
       <c r="S28"/>
     </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:19">
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -1900,7 +1717,7 @@
       <c r="R29"/>
       <c r="S29"/>
     </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:19">
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30"/>
@@ -1919,7 +1736,7 @@
       <c r="R30"/>
       <c r="S30"/>
     </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:19">
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
@@ -1938,7 +1755,7 @@
       <c r="R31"/>
       <c r="S31"/>
     </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:19">
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
@@ -1957,7 +1774,7 @@
       <c r="R32"/>
       <c r="S32"/>
     </row>
-    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:19">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1976,7 +1793,7 @@
       <c r="R33"/>
       <c r="S33"/>
     </row>
-    <row r="34" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:19">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1995,7 +1812,7 @@
       <c r="R34"/>
       <c r="S34"/>
     </row>
-    <row r="35" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:19">
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
@@ -2014,7 +1831,7 @@
       <c r="R35"/>
       <c r="S35"/>
     </row>
-    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:19">
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36"/>
@@ -2032,7 +1849,7 @@
       <c r="R36"/>
       <c r="S36"/>
     </row>
-    <row r="37" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:19">
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37"/>
@@ -2050,7 +1867,7 @@
       <c r="R37"/>
       <c r="S37"/>
     </row>
-    <row r="38" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:19">
       <c r="D38"/>
       <c r="E38"/>
       <c r="F38"/>
@@ -2068,7 +1885,7 @@
       <c r="R38"/>
       <c r="S38"/>
     </row>
-    <row r="39" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:19">
       <c r="K39"/>
       <c r="L39"/>
       <c r="M39"/>
@@ -2097,24 +1914,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD2AA26-B4D9-4C1D-9CC2-9236F00034BD}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="1"/>
+    <col min="5" max="5" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="11.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="47.25" customHeight="1">
       <c r="A1" s="23" t="s">
         <v>32</v>
       </c>
@@ -2133,7 +1950,7 @@
       <c r="K1" s="30"/>
       <c r="L1" s="30"/>
     </row>
-    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="30">
       <c r="A2" s="4" t="s">
         <v>34</v>
       </c>
@@ -2154,17 +1971,14 @@
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
     </row>
-    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="45">
       <c r="A3" s="2">
         <v>25</v>
       </c>
       <c r="B3" s="2">
         <v>50</v>
       </c>
-      <c r="C3" s="2">
-        <f>$F$12*A3+$F$13</f>
-        <v>50</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2190,169 +2004,91 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" s="2">
         <v>30</v>
       </c>
       <c r="B4" s="2">
         <v>70</v>
       </c>
-      <c r="C4" s="2">
-        <f t="shared" ref="C4:C10" si="0">$F$12*A4+$F$13</f>
-        <v>70</v>
-      </c>
-      <c r="E4" s="33">
-        <f>AVERAGE(A3:A6)</f>
-        <v>32.5</v>
-      </c>
-      <c r="F4" s="37">
-        <f>AVERAGE(B3:B6)</f>
-        <v>80</v>
-      </c>
-      <c r="G4" s="3">
-        <f>A3-$E$4</f>
-        <v>-7.5</v>
-      </c>
-      <c r="H4" s="19">
-        <f>B3-$F$4</f>
-        <v>-30</v>
-      </c>
-      <c r="I4" s="19">
-        <f>G4*H4</f>
-        <v>225</v>
-      </c>
-      <c r="J4" s="37">
-        <f>SUM(I4:I7)</f>
-        <v>500</v>
-      </c>
-      <c r="K4" s="3">
-        <f>G4*G4</f>
-        <v>56.25</v>
-      </c>
-      <c r="L4" s="33">
-        <f>SUM(K4:K7)</f>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C4" s="2"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="33"/>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="2">
         <v>35</v>
       </c>
       <c r="B5" s="2">
         <v>90</v>
       </c>
-      <c r="C5" s="2">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
+      <c r="C5" s="2"/>
       <c r="E5" s="34"/>
       <c r="F5" s="38"/>
-      <c r="G5" s="3">
-        <f t="shared" ref="G5:G7" si="1">A4-$E$4</f>
-        <v>-2.5</v>
-      </c>
-      <c r="H5" s="19">
-        <f t="shared" ref="H5:H7" si="2">B4-$F$4</f>
-        <v>-10</v>
-      </c>
-      <c r="I5" s="19">
-        <f t="shared" ref="I5:I7" si="3">G5*H5</f>
-        <v>25</v>
-      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
       <c r="J5" s="38"/>
-      <c r="K5" s="3">
-        <f t="shared" ref="K5:K7" si="4">G5*G5</f>
-        <v>6.25</v>
-      </c>
+      <c r="K5" s="3"/>
       <c r="L5" s="34"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" s="2">
         <v>40</v>
       </c>
       <c r="B6" s="2">
         <v>110</v>
       </c>
-      <c r="C6" s="2">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
+      <c r="C6" s="2"/>
       <c r="E6" s="34"/>
       <c r="F6" s="38"/>
-      <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="H6" s="19">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="I6" s="19">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
       <c r="J6" s="38"/>
-      <c r="K6" s="3">
-        <f t="shared" si="4"/>
-        <v>6.25</v>
-      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="34"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" s="3">
         <v>42</v>
       </c>
       <c r="B7" s="27">
         <v>118</v>
       </c>
-      <c r="C7" s="2">
-        <f t="shared" si="0"/>
-        <v>118</v>
-      </c>
+      <c r="C7" s="2"/>
       <c r="E7" s="35"/>
       <c r="F7" s="39"/>
-      <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>7.5</v>
-      </c>
-      <c r="H7" s="19">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="I7" s="19">
-        <f t="shared" si="3"/>
-        <v>225</v>
-      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
       <c r="J7" s="39"/>
-      <c r="K7" s="3">
-        <f t="shared" si="4"/>
-        <v>56.25</v>
-      </c>
+      <c r="K7" s="3"/>
       <c r="L7" s="35"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" s="3">
         <v>44</v>
       </c>
       <c r="B8" s="27">
         <v>126</v>
       </c>
-      <c r="C8" s="2">
-        <f t="shared" si="0"/>
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" ht="15">
       <c r="A9" s="3">
         <v>45</v>
       </c>
       <c r="B9" s="27">
         <v>130</v>
       </c>
-      <c r="C9" s="2">
-        <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
+      <c r="C9" s="2"/>
       <c r="E9" s="31" t="s">
         <v>9</v>
       </c>
@@ -2363,17 +2099,14 @@
       <c r="J9" s="31"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15">
       <c r="A10" s="3">
         <v>47</v>
       </c>
       <c r="B10" s="27">
         <v>138</v>
       </c>
-      <c r="C10" s="2">
-        <f t="shared" si="0"/>
-        <v>138</v>
-      </c>
+      <c r="C10" s="2"/>
       <c r="E10" s="31" t="s">
         <v>10</v>
       </c>
@@ -2384,31 +2117,17 @@
       <c r="J10" s="31"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15">
       <c r="E12" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="19">
-        <f>J4/L4</f>
-        <v>4</v>
-      </c>
-      <c r="G12" s="1">
-        <f>SLOPE(B3:B6,A3:A6)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F12" s="19"/>
+    </row>
+    <row r="13" spans="1:12" ht="15">
       <c r="E13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="19">
-        <f>F4-F12*E4</f>
-        <v>-50</v>
-      </c>
-      <c r="G13" s="1">
-        <f>INTERCEPT(B3:B6,A3:A6)</f>
-        <v>-50</v>
-      </c>
+      <c r="F13" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2426,409 +2145,26 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9F4249-9A10-4099-A5EF-96C04024123D}">
-  <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46914AF4-EE69-47FE-BD37-807D0CDE2794}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="1"/>
+    <col min="5" max="5" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="43"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="41">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="40">
-        <v>1</v>
-      </c>
-      <c r="C12" s="40">
-        <v>1250000000000</v>
-      </c>
-      <c r="D12" s="40">
-        <v>1250000000000</v>
-      </c>
-      <c r="E12" s="40" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="F12" s="40" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="40">
-        <v>2</v>
-      </c>
-      <c r="C13" s="40">
-        <v>0</v>
-      </c>
-      <c r="D13" s="40">
-        <v>0</v>
-      </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="41">
-        <v>3</v>
-      </c>
-      <c r="C14" s="41">
-        <v>1250000000000</v>
-      </c>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="I16" s="42" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="40">
-        <v>1000000.0000000002</v>
-      </c>
-      <c r="C17" s="40">
-        <v>0</v>
-      </c>
-      <c r="D17" s="40">
-        <v>65535</v>
-      </c>
-      <c r="E17" s="40" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="F17" s="40">
-        <v>1000000.0000000002</v>
-      </c>
-      <c r="G17" s="40">
-        <v>1000000.0000000002</v>
-      </c>
-      <c r="H17" s="40">
-        <v>1000000.0000000002</v>
-      </c>
-      <c r="I17" s="40">
-        <v>1000000.0000000002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="41">
-        <v>999.99999999999989</v>
-      </c>
-      <c r="C18" s="41">
-        <v>0</v>
-      </c>
-      <c r="D18" s="41">
-        <v>65535</v>
-      </c>
-      <c r="E18" s="41" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="F18" s="41">
-        <v>999.99999999999989</v>
-      </c>
-      <c r="G18" s="41">
-        <v>999.99999999999989</v>
-      </c>
-      <c r="H18" s="41">
-        <v>999.99999999999989</v>
-      </c>
-      <c r="I18" s="41">
-        <v>999.99999999999989</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A61215D-F91C-48D4-BE1F-34957969D662}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="43"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="40">
-        <v>2443.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="40">
-        <v>309.87288580503918</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="40">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="40" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="40">
-        <v>876.45287543435154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="40">
-        <v>768169.64285714284</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="40">
-        <v>-0.8583804351358113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="40">
-        <v>-0.57072335204024938</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="40">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="40">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" s="40">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="40">
-        <v>19550</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="40">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" s="40">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="40">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="41">
-        <v>732.73294068563723</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46914AF4-EE69-47FE-BD37-807D0CDE2794}">
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="42" customHeight="1">
       <c r="A1" s="23" t="s">
         <v>37</v>
       </c>
@@ -2847,7 +2183,7 @@
       <c r="K1" s="30"/>
       <c r="L1" s="30"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -2868,7 +2204,7 @@
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
     </row>
-    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="45">
       <c r="A3" s="2">
         <v>1000</v>
       </c>
@@ -2901,7 +2237,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" s="2">
         <v>1500</v>
       </c>
@@ -2918,7 +2254,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="33"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" s="2">
         <v>2000</v>
       </c>
@@ -2935,7 +2271,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="34"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" s="2">
         <v>2500</v>
       </c>
@@ -2952,7 +2288,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="34"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" s="3">
         <v>2800</v>
       </c>
@@ -2969,7 +2305,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="35"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" s="3">
         <v>3000</v>
       </c>
@@ -2978,7 +2314,7 @@
       </c>
       <c r="C8" s="18"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15">
       <c r="A9" s="3">
         <v>3250</v>
       </c>
@@ -2996,7 +2332,7 @@
       <c r="J9" s="31"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15">
       <c r="A10" s="3">
         <v>3500</v>
       </c>
@@ -3014,13 +2350,13 @@
       <c r="J10" s="31"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15">
       <c r="E12" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15">
       <c r="E13" s="20" t="s">
         <v>31</v>
       </c>

--- a/Excel9to10/Lec - 4.2.xlsx
+++ b/Excel9to10/Lec - 4.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllData\Excel9to10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315B7F1F-6790-40A7-A31D-8594DCD64FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F74DB1-C6E2-4CED-806C-28B7BACC260A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6C2C9399-45F9-4682-AC1B-4E221ED87509}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6C2C9399-45F9-4682-AC1B-4E221ED87509}"/>
   </bookViews>
   <sheets>
     <sheet name="Theory" sheetId="4" r:id="rId1"/>
@@ -33,9 +33,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -746,7 +743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -830,30 +827,37 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -862,14 +866,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1206,106 +1202,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BC107E-77C4-4964-9868-836DABB3D59D}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="14"/>
     </row>
-    <row r="2" spans="1:2" ht="80.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="80.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:2" ht="27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B4" s="22" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="6"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="8"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="15"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" s="15"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="39" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="39"/>
       <c r="B17" s="21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="21"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="39" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="39"/>
       <c r="B20" s="21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B22" s="5"/>
     </row>
   </sheetData>
@@ -1320,29 +1316,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4ED941-A439-4368-BF6F-884C4441C0A2}">
   <dimension ref="A1:S39"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="1"/>
+    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>14</v>
       </c>
@@ -1352,16 +1348,16 @@
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
@@ -1369,18 +1365,18 @@
         <v>17</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-    </row>
-    <row r="3" spans="1:12" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+    </row>
+    <row r="3" spans="1:12" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1415,263 +1411,164 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>8</v>
       </c>
       <c r="B4" s="16">
         <v>280</v>
       </c>
-      <c r="C4" s="18">
-        <f>$F$12*A4+$F$13</f>
-        <v>221.91588785046724</v>
-      </c>
-      <c r="E4" s="33">
-        <f>AVERAGE(A4:A7)</f>
-        <v>11.25</v>
-      </c>
-      <c r="F4" s="36">
-        <f>AVERAGE(B4:B7)</f>
-        <v>651.25</v>
-      </c>
-      <c r="G4" s="3">
-        <f>A4-$E$4</f>
-        <v>-3.25</v>
-      </c>
-      <c r="H4" s="12">
-        <f>B4-$F$4</f>
-        <v>-371.25</v>
-      </c>
-      <c r="I4" s="12">
-        <f>G4*H4</f>
-        <v>1206.5625</v>
-      </c>
-      <c r="J4" s="36">
-        <f>SUM(I4:I7)</f>
-        <v>3533.75</v>
-      </c>
-      <c r="K4" s="3">
-        <f>G4*G4</f>
-        <v>10.5625</v>
-      </c>
-      <c r="L4" s="33">
-        <f>SUM(K4:K7)</f>
-        <v>26.75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C4" s="18"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="35"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>10</v>
       </c>
       <c r="B5" s="16">
         <v>450</v>
       </c>
-      <c r="C5" s="18">
-        <f t="shared" ref="C5:C12" si="0">$F$12*A5+$F$13</f>
-        <v>486.12149532710282</v>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="3">
-        <f t="shared" ref="G5:G7" si="1">A5-$E$4</f>
-        <v>-1.25</v>
-      </c>
-      <c r="H5" s="12">
-        <f t="shared" ref="H5:H7" si="2">B5-$F$4</f>
-        <v>-201.25</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" ref="I5:I7" si="3">G5*H5</f>
-        <v>251.5625</v>
-      </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="3">
-        <f t="shared" ref="K5:K7" si="4">G5*G5</f>
-        <v>1.5625</v>
-      </c>
-      <c r="L5" s="34"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C5" s="18"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="36"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>12</v>
       </c>
       <c r="B6" s="16">
         <v>675</v>
       </c>
-      <c r="C6" s="18">
-        <f t="shared" si="0"/>
-        <v>750.32710280373817</v>
-      </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-      <c r="H6" s="12">
-        <f t="shared" si="2"/>
-        <v>23.75</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="3"/>
-        <v>17.8125</v>
-      </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="3">
-        <f t="shared" si="4"/>
-        <v>0.5625</v>
-      </c>
-      <c r="L6" s="34"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C6" s="18"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="36"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>15</v>
       </c>
       <c r="B7" s="16">
         <v>1200</v>
       </c>
-      <c r="C7" s="18">
-        <f t="shared" si="0"/>
-        <v>1146.6355140186915</v>
-      </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>3.75</v>
-      </c>
-      <c r="H7" s="12">
-        <f t="shared" si="2"/>
-        <v>548.75</v>
-      </c>
-      <c r="I7" s="12">
-        <f t="shared" si="3"/>
-        <v>2057.8125</v>
-      </c>
-      <c r="J7" s="35"/>
-      <c r="K7" s="3">
-        <f t="shared" si="4"/>
-        <v>14.0625</v>
-      </c>
-      <c r="L7" s="35"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C7" s="18"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="37"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>17</v>
       </c>
       <c r="B8" s="26">
         <v>1410.8411214953269</v>
       </c>
-      <c r="C8" s="18">
-        <f t="shared" si="0"/>
-        <v>1410.8411214953269</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C8" s="18"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>18</v>
       </c>
       <c r="B9" s="26">
         <v>1542.9439252336449</v>
       </c>
-      <c r="C9" s="18">
-        <f t="shared" si="0"/>
-        <v>1542.9439252336449</v>
-      </c>
-      <c r="E9" s="31" t="s">
+      <c r="C9" s="18"/>
+      <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>20</v>
       </c>
       <c r="B10" s="26">
         <v>1807.1495327102805</v>
       </c>
-      <c r="C10" s="18">
-        <f t="shared" si="0"/>
-        <v>1807.1495327102805</v>
-      </c>
-      <c r="E10" s="31" t="s">
+      <c r="C10" s="18"/>
+      <c r="E10" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>22</v>
       </c>
       <c r="B11" s="26">
         <v>2071.3551401869163</v>
       </c>
-      <c r="C11" s="18">
-        <f t="shared" si="0"/>
-        <v>2071.3551401869163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C11" s="18"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>26</v>
       </c>
       <c r="B12" s="26">
         <v>2599.7663551401865</v>
       </c>
-      <c r="C12" s="18">
-        <f t="shared" si="0"/>
-        <v>2599.7663551401865</v>
-      </c>
+      <c r="C12" s="18"/>
       <c r="E12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="12">
-        <f>J4/L4</f>
-        <v>132.10280373831776</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E13" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="28">
-        <f>F4-F12*E4</f>
-        <v>-834.90654205607484</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F13" s="28"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E16" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="12">
-        <f>SLOPE(B4:B7,A4:A7)</f>
-        <v>132.10280373831776</v>
-      </c>
+      <c r="F16" s="12"/>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
     </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="12">
-        <f>INTERCEPT(B4:B7,A4:A7)</f>
-        <v>-834.90654205607484</v>
-      </c>
+      <c r="F17" s="12"/>
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17"/>
@@ -1679,7 +1576,7 @@
       <c r="K17"/>
       <c r="L17"/>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18"/>
@@ -1691,7 +1588,7 @@
       <c r="K18"/>
       <c r="L18"/>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
@@ -1710,7 +1607,7 @@
       <c r="R19"/>
       <c r="S19"/>
     </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
@@ -1729,7 +1626,7 @@
       <c r="R20"/>
       <c r="S20"/>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
@@ -1748,7 +1645,7 @@
       <c r="R21"/>
       <c r="S21"/>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
@@ -1767,7 +1664,7 @@
       <c r="R22"/>
       <c r="S22"/>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
@@ -1786,7 +1683,7 @@
       <c r="R23"/>
       <c r="S23"/>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
@@ -1805,7 +1702,7 @@
       <c r="R24"/>
       <c r="S24"/>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25"/>
@@ -1824,7 +1721,7 @@
       <c r="R25"/>
       <c r="S25"/>
     </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -1843,7 +1740,7 @@
       <c r="R26"/>
       <c r="S26"/>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -1862,7 +1759,7 @@
       <c r="R27"/>
       <c r="S27"/>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -1881,7 +1778,7 @@
       <c r="R28"/>
       <c r="S28"/>
     </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -1900,7 +1797,7 @@
       <c r="R29"/>
       <c r="S29"/>
     </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30"/>
@@ -1919,7 +1816,7 @@
       <c r="R30"/>
       <c r="S30"/>
     </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
@@ -1938,7 +1835,7 @@
       <c r="R31"/>
       <c r="S31"/>
     </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
@@ -1957,7 +1854,7 @@
       <c r="R32"/>
       <c r="S32"/>
     </row>
-    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1976,7 +1873,7 @@
       <c r="R33"/>
       <c r="S33"/>
     </row>
-    <row r="34" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1995,7 +1892,7 @@
       <c r="R34"/>
       <c r="S34"/>
     </row>
-    <row r="35" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
@@ -2014,7 +1911,7 @@
       <c r="R35"/>
       <c r="S35"/>
     </row>
-    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:19" x14ac:dyDescent="0.3">
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36"/>
@@ -2032,7 +1929,7 @@
       <c r="R36"/>
       <c r="S36"/>
     </row>
-    <row r="37" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:19" x14ac:dyDescent="0.3">
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37"/>
@@ -2050,7 +1947,7 @@
       <c r="R37"/>
       <c r="S37"/>
     </row>
-    <row r="38" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:19" x14ac:dyDescent="0.3">
       <c r="D38"/>
       <c r="E38"/>
       <c r="F38"/>
@@ -2068,7 +1965,7 @@
       <c r="R38"/>
       <c r="S38"/>
     </row>
-    <row r="39" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:19" x14ac:dyDescent="0.3">
       <c r="K39"/>
       <c r="L39"/>
       <c r="M39"/>
@@ -2097,24 +1994,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD2AA26-B4D9-4C1D-9CC2-9236F00034BD}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="1"/>
+    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="11.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>32</v>
       </c>
@@ -2124,16 +2021,16 @@
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-    </row>
-    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+    </row>
+    <row r="2" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>34</v>
       </c>
@@ -2143,28 +2040,25 @@
       <c r="C2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-    </row>
-    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+    </row>
+    <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>25</v>
       </c>
       <c r="B3" s="2">
         <v>50</v>
       </c>
-      <c r="C3" s="2">
-        <f>$F$12*A3+$F$13</f>
-        <v>50</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2190,225 +2084,130 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>30</v>
       </c>
       <c r="B4" s="2">
         <v>70</v>
       </c>
-      <c r="C4" s="2">
-        <f t="shared" ref="C4:C10" si="0">$F$12*A4+$F$13</f>
-        <v>70</v>
-      </c>
-      <c r="E4" s="33">
-        <f>AVERAGE(A3:A6)</f>
-        <v>32.5</v>
-      </c>
-      <c r="F4" s="37">
-        <f>AVERAGE(B3:B6)</f>
-        <v>80</v>
-      </c>
-      <c r="G4" s="3">
-        <f>A3-$E$4</f>
-        <v>-7.5</v>
-      </c>
-      <c r="H4" s="19">
-        <f>B3-$F$4</f>
-        <v>-30</v>
-      </c>
-      <c r="I4" s="19">
-        <f>G4*H4</f>
-        <v>225</v>
-      </c>
-      <c r="J4" s="37">
-        <f>SUM(I4:I7)</f>
-        <v>500</v>
-      </c>
-      <c r="K4" s="3">
-        <f>G4*G4</f>
-        <v>56.25</v>
-      </c>
-      <c r="L4" s="33">
-        <f>SUM(K4:K7)</f>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C4" s="2"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="35"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>35</v>
       </c>
       <c r="B5" s="2">
         <v>90</v>
       </c>
-      <c r="C5" s="2">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="3">
-        <f t="shared" ref="G5:G7" si="1">A4-$E$4</f>
-        <v>-2.5</v>
-      </c>
-      <c r="H5" s="19">
-        <f t="shared" ref="H5:H7" si="2">B4-$F$4</f>
-        <v>-10</v>
-      </c>
-      <c r="I5" s="19">
-        <f t="shared" ref="I5:I7" si="3">G5*H5</f>
-        <v>25</v>
-      </c>
-      <c r="J5" s="38"/>
-      <c r="K5" s="3">
-        <f t="shared" ref="K5:K7" si="4">G5*G5</f>
-        <v>6.25</v>
-      </c>
-      <c r="L5" s="34"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C5" s="2"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="36"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>40</v>
       </c>
       <c r="B6" s="2">
         <v>110</v>
       </c>
-      <c r="C6" s="2">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="H6" s="19">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="I6" s="19">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="3">
-        <f t="shared" si="4"/>
-        <v>6.25</v>
-      </c>
-      <c r="L6" s="34"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C6" s="2"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="36"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>42</v>
       </c>
       <c r="B7" s="27">
         <v>118</v>
       </c>
-      <c r="C7" s="2">
-        <f t="shared" si="0"/>
-        <v>118</v>
-      </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>7.5</v>
-      </c>
-      <c r="H7" s="19">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="I7" s="19">
-        <f t="shared" si="3"/>
-        <v>225</v>
-      </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="3">
-        <f t="shared" si="4"/>
-        <v>56.25</v>
-      </c>
-      <c r="L7" s="35"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C7" s="2"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="37"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>44</v>
       </c>
       <c r="B8" s="27">
         <v>126</v>
       </c>
-      <c r="C8" s="2">
-        <f t="shared" si="0"/>
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>45</v>
       </c>
       <c r="B9" s="27">
         <v>130</v>
       </c>
-      <c r="C9" s="2">
-        <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
-      <c r="E9" s="31" t="s">
+      <c r="C9" s="2"/>
+      <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>47</v>
       </c>
       <c r="B10" s="27">
         <v>138</v>
       </c>
-      <c r="C10" s="2">
-        <f t="shared" si="0"/>
-        <v>138</v>
-      </c>
-      <c r="E10" s="31" t="s">
+      <c r="C10" s="2"/>
+      <c r="E10" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E12" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="19">
-        <f>J4/L4</f>
-        <v>4</v>
-      </c>
-      <c r="G12" s="1">
-        <f>SLOPE(B3:B6,A3:A6)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F12" s="19"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="19">
-        <f>F4-F12*E4</f>
-        <v>-50</v>
-      </c>
-      <c r="G13" s="1">
-        <f>INTERCEPT(B3:B6,A3:A6)</f>
-        <v>-50</v>
-      </c>
+      <c r="F13" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2428,226 +2227,224 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9F4249-9A10-4099-A5EF-96C04024123D}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="43"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="B3" s="31"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="40">
+      <c r="B5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="41" t="s">
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="41">
+      <c r="B8" s="29">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="30" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12">
         <v>1250000000000</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12">
         <v>1250000000000</v>
       </c>
-      <c r="E12" s="40" t="e">
+      <c r="E12" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F12" s="40" t="e">
+      <c r="F12" t="e">
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="40">
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13">
         <v>0</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13">
         <v>0</v>
       </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="41">
+      <c r="B14" s="29">
         <v>3</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="29">
         <v>1250000000000</v>
       </c>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42" t="s">
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="30"/>
+      <c r="B16" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="42" t="s">
+      <c r="F16" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="42" t="s">
+      <c r="G16" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="42" t="s">
+      <c r="I16" s="30" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="40">
+      <c r="B17">
         <v>1000000.0000000002</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17">
         <v>0</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17">
         <v>65535</v>
       </c>
-      <c r="E17" s="40" t="e">
+      <c r="E17" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17">
         <v>1000000.0000000002</v>
       </c>
-      <c r="G17" s="40">
+      <c r="G17">
         <v>1000000.0000000002</v>
       </c>
-      <c r="H17" s="40">
+      <c r="H17">
         <v>1000000.0000000002</v>
       </c>
-      <c r="I17" s="40">
+      <c r="I17">
         <v>1000000.0000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
+    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="29">
         <v>999.99999999999989</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="29">
         <v>0</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="29">
         <v>65535</v>
       </c>
-      <c r="E18" s="41" t="e">
+      <c r="E18" s="29" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="29">
         <v>999.99999999999989</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="29">
         <v>999.99999999999989</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="29">
         <v>999.99999999999989</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="29">
         <v>999.99999999999989</v>
       </c>
     </row>
@@ -2659,147 +2456,143 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A61215D-F91C-48D4-BE1F-34957969D662}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="43"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="B1" s="31"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="40">
+      <c r="B3">
         <v>2443.75</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B4">
         <v>309.87288580503918</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="40">
+      <c r="B5">
         <v>2650</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="40" t="e">
+      <c r="B6" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7">
         <v>876.45287543435154</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="40">
+      <c r="B8">
         <v>768169.64285714284</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9">
         <v>-0.8583804351358113</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="40">
+      <c r="B10">
         <v>-0.57072335204024938</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="40">
+      <c r="B11">
         <v>2500</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12">
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="40">
+      <c r="B13">
         <v>3500</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="40">
+      <c r="B14">
         <v>19550</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="40">
+      <c r="B15">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="40">
+      <c r="B16">
         <v>3500</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="40">
+      <c r="B17">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
+    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="29">
         <v>732.73294068563723</v>
       </c>
     </row>
@@ -2811,24 +2604,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46914AF4-EE69-47FE-BD37-807D0CDE2794}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="1"/>
+    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>37</v>
       </c>
@@ -2838,16 +2631,16 @@
       <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -2857,18 +2650,18 @@
       <c r="C2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-    </row>
-    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+    </row>
+    <row r="3" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1000</v>
       </c>
@@ -2901,7 +2694,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1500</v>
       </c>
@@ -2909,16 +2702,16 @@
         <v>2500000</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="36"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="38"/>
       <c r="G4" s="3"/>
       <c r="H4" s="25"/>
       <c r="I4" s="12"/>
-      <c r="J4" s="36"/>
+      <c r="J4" s="38"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="33"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="35"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2000</v>
       </c>
@@ -2926,16 +2719,16 @@
         <v>3000000</v>
       </c>
       <c r="C5" s="18"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
       <c r="G5" s="3"/>
       <c r="H5" s="25"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="34"/>
+      <c r="J5" s="36"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="34"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L5" s="36"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2500</v>
       </c>
@@ -2943,16 +2736,16 @@
         <v>3500000</v>
       </c>
       <c r="C6" s="18"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
       <c r="G6" s="3"/>
       <c r="H6" s="25"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="34"/>
+      <c r="J6" s="36"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="34"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="36"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>2800</v>
       </c>
@@ -2960,16 +2753,16 @@
         <v>3800000</v>
       </c>
       <c r="C7" s="18"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
       <c r="G7" s="3"/>
       <c r="H7" s="25"/>
       <c r="I7" s="12"/>
-      <c r="J7" s="35"/>
+      <c r="J7" s="37"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="35"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L7" s="37"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>3000</v>
       </c>
@@ -2978,7 +2771,7 @@
       </c>
       <c r="C8" s="18"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>3250</v>
       </c>
@@ -2986,17 +2779,17 @@
         <v>4250000</v>
       </c>
       <c r="C9" s="18"/>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>3500</v>
       </c>
@@ -3004,23 +2797,23 @@
         <v>4500000</v>
       </c>
       <c r="C10" s="18"/>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E12" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E13" s="20" t="s">
         <v>31</v>
       </c>
